--- a/data/10Maj-89ers-v-Oaks.xlsx
+++ b/data/10Maj-89ers-v-Oaks.xlsx
@@ -190,7 +190,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:O133"/>
   <sheetData>
     <row r="1">
@@ -844,8 +844,10 @@
       <c r="D68" t="s">
         <v>18</v>
       </c>
-      <c r="E68" t="s">
-        <v>31</v>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>UCDCLC</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -923,8 +925,10 @@
       <c r="D76" t="s">
         <v>18</v>
       </c>
-      <c r="E76" t="s">
-        <v>34</v>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>DCLC</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -1392,8 +1396,10 @@
       <c r="D123" t="s">
         <v>52</v>
       </c>
-      <c r="E123" t="s">
-        <v>53</v>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>RNDN</t>
+        </is>
       </c>
       <c r="I123" t="s">
         <v>54</v>
